--- a/public/formats/item_price_lists.xlsx
+++ b/public/formats/item_price_lists.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sdrimsac_final\public\formats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sdrimsac-tenant\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C93B365-8017-44D6-A8A7-B9CB4AC14D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Código Tipo de Unidad</t>
   </si>
@@ -49,12 +48,21 @@
   </si>
   <si>
     <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Precio1</t>
+  </si>
+  <si>
+    <t>Precio2</t>
+  </si>
+  <si>
+    <t>Precio3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -365,8 +373,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -374,7 +382,7 @@
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -390,8 +398,17 @@
       <c r="E1" t="s">
         <v>6</v>
       </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
